--- a/data/grondwater_template.xlsx
+++ b/data/grondwater_template.xlsx
@@ -4650,7 +4650,7 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2024-07-24 08:59:59.779297</t>
+    <t>2024-07-24 09:03:31.065121</t>
   </si>
   <si>
     <t>version</t>
